--- a/selenium/tastcase/cleaned_data.xlsx
+++ b/selenium/tastcase/cleaned_data.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\python_Automation\selenium\tastcase\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F22ADC-55CC-49DD-9209-1994B117D5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -436,11 +442,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,13 +510,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -548,7 +562,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -582,6 +596,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -616,9 +631,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -791,11 +807,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N92"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -839,7 +866,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -880,7 +907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -924,7 +951,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -965,7 +992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1006,7 +1033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1047,7 +1074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1091,7 +1118,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -1132,7 +1159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1176,7 +1203,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1220,7 +1247,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1261,7 +1288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -1302,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1346,7 +1373,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1390,7 +1417,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1434,7 +1461,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1475,7 +1502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1519,7 +1546,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1563,7 +1590,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -1604,7 +1631,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1648,7 +1675,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -1692,7 +1719,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1733,7 +1760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -1777,7 +1804,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1821,7 +1848,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -1865,7 +1892,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1909,7 +1936,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1950,7 +1977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1991,7 +2018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -2035,7 +2062,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -2076,7 +2103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -2117,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>44</v>
       </c>
@@ -2161,7 +2188,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -2202,7 +2229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -2246,7 +2273,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -2287,7 +2314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -2328,7 +2355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -2369,7 +2396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>50</v>
       </c>
@@ -2410,7 +2437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -2451,7 +2478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -2492,7 +2519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -2536,7 +2563,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>54</v>
       </c>
@@ -2580,7 +2607,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>55</v>
       </c>
@@ -2624,7 +2651,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -2665,7 +2692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>57</v>
       </c>
@@ -2706,7 +2733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>58</v>
       </c>
@@ -2750,7 +2777,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -2791,7 +2818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -2835,7 +2862,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -2876,7 +2903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>62</v>
       </c>
@@ -2917,7 +2944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -2958,7 +2985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>64</v>
       </c>
@@ -2999,7 +3026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>65</v>
       </c>
@@ -3043,7 +3070,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>66</v>
       </c>
@@ -3087,7 +3114,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>67</v>
       </c>
@@ -3128,7 +3155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -3172,7 +3199,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -3213,7 +3240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -3257,7 +3284,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>71</v>
       </c>
@@ -3298,7 +3325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>72</v>
       </c>
@@ -3339,7 +3366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>73</v>
       </c>
@@ -3383,7 +3410,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -3427,7 +3454,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>75</v>
       </c>
@@ -3471,7 +3498,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -3512,7 +3539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -3553,7 +3580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>78</v>
       </c>
@@ -3594,7 +3621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>79</v>
       </c>
@@ -3635,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>80</v>
       </c>
@@ -3679,7 +3706,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -3699,7 +3726,7 @@
         <v>2</v>
       </c>
       <c r="G69">
-        <v>2535.3</v>
+        <v>2535.3000000000002</v>
       </c>
       <c r="H69">
         <v>19</v>
@@ -3723,7 +3750,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>82</v>
       </c>
@@ -3767,7 +3794,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -3808,7 +3835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -3852,7 +3879,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -3896,7 +3923,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>86</v>
       </c>
@@ -3937,7 +3964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -3981,7 +4008,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>88</v>
       </c>
@@ -4025,7 +4052,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>89</v>
       </c>
@@ -4066,7 +4093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>90</v>
       </c>
@@ -4110,7 +4137,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -4151,7 +4178,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -4195,7 +4222,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>93</v>
       </c>
@@ -4239,7 +4266,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>94</v>
       </c>
@@ -4280,7 +4307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>95</v>
       </c>
@@ -4300,7 +4327,7 @@
         <v>3</v>
       </c>
       <c r="G83">
-        <v>1219.86</v>
+        <v>1219.8599999999999</v>
       </c>
       <c r="H83">
         <v>19</v>
@@ -4321,7 +4348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>96</v>
       </c>
@@ -4362,7 +4389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -4406,7 +4433,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>98</v>
       </c>
@@ -4447,7 +4474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -4488,7 +4515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>100</v>
       </c>
@@ -4532,7 +4559,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>101</v>
       </c>
@@ -4576,7 +4603,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>102</v>
       </c>
@@ -4620,7 +4647,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -4664,7 +4691,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>104</v>
       </c>
